--- a/PRD/DRMS_PRD_v10.xlsx
+++ b/PRD/DRMS_PRD_v10.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="p69cowMLedSQpoas5d7J/loMLgcjiSTa0MTxuX6E0sg="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="a8raXZ4/3sFgAh59GD25JNJhEae+SYvHvc+fHAtMJ0o="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="296">
   <si>
     <t xml:space="preserve">Product Requirement Document (PRD)  For  Disaster Relief Management System (DRMS)  </t>
   </si>
@@ -81,13 +81,10 @@
     <t>Acceptance Criteria</t>
   </si>
   <si>
-    <t xml:space="preserve">  Authentication</t>
-  </si>
-  <si>
     <t>FR-01</t>
   </si>
   <si>
-    <t>User Registration</t>
+    <t>User Registration [Admin] [Volunteer] [Donor]</t>
   </si>
   <si>
     <t>Register users with roles</t>
@@ -117,7 +114,7 @@
     <t>FR-02</t>
   </si>
   <si>
-    <t>User Login</t>
+    <t xml:space="preserve">User Login [Admin] [Volunteer] [Donor] </t>
   </si>
   <si>
     <t>Secure login system</t>
@@ -144,7 +141,7 @@
     <t>FR-03</t>
   </si>
   <si>
-    <t>Forgot Password</t>
+    <t>Forgot Password [Admin] [Volunteer] [Donor] [Affected Person]</t>
   </si>
   <si>
     <t>Reset password using OTP</t>
@@ -171,7 +168,7 @@
     <t>FR-04</t>
   </si>
   <si>
-    <t>Email Verification</t>
+    <t>Email Verification [Admin] [Volunteer] [Donor] [Affected Person]</t>
   </si>
   <si>
     <t>Verify user email</t>
@@ -194,7 +191,7 @@
     <t>FR-05</t>
   </si>
   <si>
-    <t>Profile Manage</t>
+    <t>Profile Manage [Admin] [Volunteer] [Donor] [Affected Person]</t>
   </si>
   <si>
     <t>update user profile</t>
@@ -219,7 +216,7 @@
     <t>FR-06</t>
   </si>
   <si>
-    <t>Theme Change</t>
+    <t>Theme Change [Admin] [Volunteer] [Donor] [Affected Person]</t>
   </si>
   <si>
     <t>Toggle Light&amp;Dark mode</t>
@@ -239,7 +236,7 @@
     <t>FR-07</t>
   </si>
   <si>
-    <t>Language Change</t>
+    <t>Language Change [Admin] [Volunteer] [Donor] [Affected Person]</t>
   </si>
   <si>
     <t>Switch language</t>
@@ -259,13 +256,10 @@
 • Fallback to English if unsupported</t>
   </si>
   <si>
-    <t xml:space="preserve">  Admin</t>
-  </si>
-  <si>
     <t>FR-08</t>
   </si>
   <si>
-    <t>Admin Dashboard</t>
+    <t>Admin Dashboard [Admin]</t>
   </si>
   <si>
     <t>System overview</t>
@@ -290,7 +284,7 @@
     <t>FR-09</t>
   </si>
   <si>
-    <t>Manage Relief Camps</t>
+    <t>Manage Relief Camps [Admin]</t>
   </si>
   <si>
     <t>Add/Edit/Delete camps</t>
@@ -318,7 +312,7 @@
     <t>FR-10</t>
   </si>
   <si>
-    <t>Resource Allocation</t>
+    <t xml:space="preserve">Resource Allocation [Admin] </t>
   </si>
   <si>
     <t>Allocate resources</t>
@@ -345,7 +339,7 @@
     <t>FR-11</t>
   </si>
   <si>
-    <t>Reports &amp; Analytics</t>
+    <t xml:space="preserve">Reports &amp; Analytics [Admin] </t>
   </si>
   <si>
     <t>View system reports</t>
@@ -369,7 +363,7 @@
     <t>FR-12</t>
   </si>
   <si>
-    <t>Export Reports</t>
+    <t>Export Reports [Admin]</t>
   </si>
   <si>
     <t>Download reports</t>
@@ -391,7 +385,7 @@
     <t>FR-13</t>
   </si>
   <si>
-    <t>Manage Users</t>
+    <t xml:space="preserve">Manage Users [Admin] </t>
   </si>
   <si>
     <t>Activate/Deactivate users</t>
@@ -415,13 +409,10 @@
 • Audit log must record action</t>
   </si>
   <si>
-    <t xml:space="preserve">  Volunteer</t>
-  </si>
-  <si>
     <t>FR-14</t>
   </si>
   <si>
-    <t>Volunteer Dashboard</t>
+    <t xml:space="preserve">Volunteer Dashboard [Volunteer] </t>
   </si>
   <si>
     <t>View assigned tasks</t>
@@ -444,7 +435,7 @@
     <t>FR-15</t>
   </si>
   <si>
-    <t>Task Assignment</t>
+    <t xml:space="preserve">Task Assignment [Admin] </t>
   </si>
   <si>
     <t>Assign tasks to volunteers</t>
@@ -470,7 +461,7 @@
     <t>FR-16</t>
   </si>
   <si>
-    <t>Task Status Update</t>
+    <t xml:space="preserve">Task Status Update  [Volunteer] </t>
   </si>
   <si>
     <t>Update task progress</t>
@@ -493,7 +484,7 @@
     <t>FR-17</t>
   </si>
   <si>
-    <t>Shift Management</t>
+    <t xml:space="preserve">Shift Management[Volunteer] </t>
   </si>
   <si>
     <t>Manage work shifts</t>
@@ -517,7 +508,7 @@
     <t>FR-18</t>
   </si>
   <si>
-    <t>Performance Tracking</t>
+    <t xml:space="preserve">Performance Tracking [Admin] </t>
   </si>
   <si>
     <t>Track volunteer performance</t>
@@ -539,13 +530,10 @@
 • Summary metrics displayed clearly</t>
   </si>
   <si>
-    <t xml:space="preserve">  Affected Person</t>
-  </si>
-  <si>
     <t>FR-19</t>
   </si>
   <si>
-    <t>Affected Person Registration</t>
+    <t>Affected Person Registration [Affected Person]</t>
   </si>
   <si>
     <t>Register affected users</t>
@@ -572,7 +560,7 @@
     <t>FR-20</t>
   </si>
   <si>
-    <t>Aid Request Submission</t>
+    <t>Aid Request Submission  [Affected Person]</t>
   </si>
   <si>
     <t>Request aid</t>
@@ -596,7 +584,7 @@
     <t>FR-21</t>
   </si>
   <si>
-    <t>Face Recognition for Aid Registration</t>
+    <t>Face Recognition for Aid Registration  [Affected Person]</t>
   </si>
   <si>
     <t>Capture and verify faces of all family members during aid request submission</t>
@@ -632,7 +620,7 @@
     <t>FR-22</t>
   </si>
   <si>
-    <t xml:space="preserve"> Family Member Verification History</t>
+    <t xml:space="preserve"> Family Member Verification History [Admin] </t>
   </si>
   <si>
     <t>Track and display verification history of all family members with timestamps and verification status</t>
@@ -663,7 +651,7 @@
     <t>FR-23</t>
   </si>
   <si>
-    <t xml:space="preserve"> Biometric Fraud Detection &amp; Alert System</t>
+    <t xml:space="preserve"> Biometric Fraud Detection &amp; Alert System [Admin] </t>
   </si>
   <si>
     <t xml:space="preserve"> Real-time detection of duplicate face registrations across multiple aid requests with automatic admin alerts</t>
@@ -698,7 +686,7 @@
     <t>FR-24</t>
   </si>
   <si>
-    <t>Aid Request Tracking</t>
+    <t>Aid Request Tracking  [Affected Person]</t>
   </si>
   <si>
     <t>Track aid status</t>
@@ -723,7 +711,7 @@
     <t>FR-25</t>
   </si>
   <si>
-    <t>Camp Suggestion</t>
+    <t>Camp Suggestion  [Affected Person]</t>
   </si>
   <si>
     <t>Suggest nearest camp</t>
@@ -741,13 +729,10 @@
 • Response within 2 seconds</t>
   </si>
   <si>
-    <t xml:space="preserve">  Donor</t>
-  </si>
-  <si>
     <t>FR-26</t>
   </si>
   <si>
-    <t>Donation System</t>
+    <t>Donation Form [Donor]</t>
   </si>
   <si>
     <t>Donate money or goods</t>
@@ -772,7 +757,7 @@
     <t>FR-27</t>
   </si>
   <si>
-    <t>Payment Integration</t>
+    <t xml:space="preserve">Payment Integration  [Donor] </t>
   </si>
   <si>
     <t>Process payments</t>
@@ -796,7 +781,7 @@
     <t>FR-28</t>
   </si>
   <si>
-    <t>Donation Tracking</t>
+    <t>Donation Tracking  [Donor]</t>
   </si>
   <si>
     <t>Track donations</t>
@@ -818,13 +803,10 @@
 • No missing entries</t>
   </si>
   <si>
-    <t xml:space="preserve">  Notification</t>
-  </si>
-  <si>
     <t>FR-29</t>
   </si>
   <si>
-    <t>Notification System</t>
+    <t>Notification System [Admin] [Volunteer] [Donor] [Affected Person]</t>
   </si>
   <si>
     <t>Send alerts</t>
@@ -847,7 +829,7 @@
     <t>FR-30</t>
   </si>
   <si>
-    <t>Emergency Alerts</t>
+    <t xml:space="preserve">Emergency Alerts Announcement [Admin] </t>
   </si>
   <si>
     <t>Broadcast alerts</t>
@@ -865,6 +847,9 @@
 • No delivery failure</t>
   </si>
   <si>
+    <t xml:space="preserve">  </t>
+  </si>
+  <si>
     <t xml:space="preserve">  Non-Functional Requirements</t>
   </si>
   <si>
@@ -1124,9 +1109,6 @@
   </si>
   <si>
     <t>NFR-19</t>
-  </si>
-  <si>
-    <t>Compliance</t>
   </si>
   <si>
     <t>Data Privacy</t>
@@ -1154,7 +1136,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="16">
+  <fonts count="8">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -1164,7 +1146,7 @@
     <font>
       <b/>
       <sz val="13.0"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font/>
@@ -1175,38 +1157,14 @@
     </font>
     <font>
       <b/>
-      <sz val="8.0"/>
+      <sz val="12.0"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="12.0"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="7.0"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12.0"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11.0"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10.0"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
       <color rgb="FFFFFFFF"/>
@@ -1214,34 +1172,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.0"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="8.0"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="9.0"/>
-      <color rgb="FFF3F3F3"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <color rgb="FF1F3864"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10.0"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <sz val="12.0"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1250,44 +1186,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F3864"/>
-        <bgColor rgb="FF1F3864"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9E1F2"/>
-        <bgColor rgb="FFD9E1F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2E4057"/>
-        <bgColor rgb="FF2E4057"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEAF4FB"/>
-        <bgColor rgb="FFEAF4FB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0FFF0"/>
-        <bgColor rgb="FFF0FFF0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFBE6"/>
-        <bgColor rgb="FFFFFBE6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF0F0"/>
-        <bgColor rgb="FFFFF0F0"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -1298,42 +1198,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0EAFF"/>
-        <bgColor rgb="FFF0EAFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF0E6"/>
-        <bgColor rgb="FFFFF0E6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF000000"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCE4D6"/>
-        <bgColor rgb="FFFCE4D6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor rgb="FFFFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FF1F3864"/>
+        <bgColor rgb="FF1F3864"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="8">
     <border/>
     <border>
       <left style="thin">
@@ -1386,21 +1256,32 @@
       <bottom/>
     </border>
     <border>
-      <left/>
-      <top/>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
     </border>
     <border>
-      <top/>
-    </border>
-    <border>
-      <right/>
-      <top/>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="28">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1410,107 +1291,65 @@
     <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="4" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="4" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="3" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="4" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="6" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="3" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="4" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="6" fillId="4" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="7" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="8" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="4" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="7" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="8" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="9" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="9" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="9" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="9" fontId="10" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="9" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="9" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="9" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="9" fontId="10" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="4" fillId="8" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="4" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="4" fontId="14" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="2" fillId="4" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="4" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="4" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="4" fillId="10" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="10" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="2" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="2" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="2" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="4" fillId="11" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="11" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="7" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="12" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="13" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="14" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="15" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
+    <xf borderId="0" fillId="2" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="2" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -1826,7 +1665,7 @@
       <c r="Z3" s="4"/>
     </row>
     <row r="4" ht="19.5" customHeight="1">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="5" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="6"/>
@@ -1984,12 +1823,14 @@
       <c r="Z8" s="4"/>
     </row>
     <row r="9" ht="19.5" customHeight="1">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
+      <c r="A9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="3"/>
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
       <c r="I9" s="4"/>
@@ -2012,14 +1853,24 @@
       <c r="Z9" s="4"/>
     </row>
     <row r="10" ht="19.5" customHeight="1">
-      <c r="A10" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="3"/>
+      <c r="A10" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>20</v>
+      </c>
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
       <c r="I10" s="4"/>
@@ -2041,24 +1892,24 @@
       <c r="Y10" s="4"/>
       <c r="Z10" s="4"/>
     </row>
-    <row r="11" ht="19.5" customHeight="1">
-      <c r="A11" s="10" t="s">
-        <v>15</v>
+    <row r="11" ht="120.0" customHeight="1">
+      <c r="A11" s="9" t="s">
+        <v>21</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>26</v>
       </c>
       <c r="G11" s="4"/>
       <c r="H11" s="4"/>
@@ -2081,15 +1932,25 @@
       <c r="Y11" s="4"/>
       <c r="Z11" s="4"/>
     </row>
-    <row r="12" ht="19.5" customHeight="1">
-      <c r="A12" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12" s="12"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="13"/>
+    <row r="12" ht="75.0" customHeight="1">
+      <c r="A12" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>32</v>
+      </c>
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
@@ -2111,24 +1972,24 @@
       <c r="Y12" s="4"/>
       <c r="Z12" s="4"/>
     </row>
-    <row r="13" ht="120.0" customHeight="1">
-      <c r="A13" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="F13" s="14" t="s">
-        <v>27</v>
+    <row r="13" ht="105.0" customHeight="1">
+      <c r="A13" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>38</v>
       </c>
       <c r="G13" s="4"/>
       <c r="H13" s="4"/>
@@ -2151,24 +2012,24 @@
       <c r="Y13" s="4"/>
       <c r="Z13" s="4"/>
     </row>
-    <row r="14" ht="75.0" customHeight="1">
-      <c r="A14" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="B14" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="D14" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="E14" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="F14" s="14" t="s">
-        <v>33</v>
+    <row r="14" ht="60.0" customHeight="1">
+      <c r="A14" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>44</v>
       </c>
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
@@ -2191,24 +2052,24 @@
       <c r="Y14" s="4"/>
       <c r="Z14" s="4"/>
     </row>
-    <row r="15" ht="105.0" customHeight="1">
-      <c r="A15" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="B15" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="C15" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="D15" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="E15" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="F15" s="14" t="s">
-        <v>39</v>
+    <row r="15" ht="90.0" customHeight="1">
+      <c r="A15" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>50</v>
       </c>
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
@@ -2231,24 +2092,24 @@
       <c r="Y15" s="4"/>
       <c r="Z15" s="4"/>
     </row>
-    <row r="16" ht="60.0" customHeight="1">
-      <c r="A16" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="B16" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="C16" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="D16" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="E16" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="F16" s="14" t="s">
-        <v>45</v>
+    <row r="16" ht="45.0" customHeight="1">
+      <c r="A16" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>56</v>
       </c>
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
@@ -2271,24 +2132,24 @@
       <c r="Y16" s="4"/>
       <c r="Z16" s="4"/>
     </row>
-    <row r="17" ht="90.0" customHeight="1">
-      <c r="A17" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B17" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="C17" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="D17" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="E17" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="F17" s="14" t="s">
-        <v>51</v>
+    <row r="17" ht="60.0" customHeight="1">
+      <c r="A17" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>62</v>
       </c>
       <c r="G17" s="4"/>
       <c r="H17" s="4"/>
@@ -2311,24 +2172,24 @@
       <c r="Y17" s="4"/>
       <c r="Z17" s="4"/>
     </row>
-    <row r="18" ht="45.0" customHeight="1">
-      <c r="A18" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="B18" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="C18" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="D18" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="E18" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="F18" s="14" t="s">
-        <v>57</v>
+    <row r="18" ht="75.0" customHeight="1">
+      <c r="A18" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>68</v>
       </c>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
@@ -2351,24 +2212,24 @@
       <c r="Y18" s="4"/>
       <c r="Z18" s="4"/>
     </row>
-    <row r="19" ht="60.0" customHeight="1">
-      <c r="A19" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="B19" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C19" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="D19" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="E19" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="F19" s="14" t="s">
-        <v>63</v>
+    <row r="19" ht="120.0" customHeight="1">
+      <c r="A19" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>74</v>
       </c>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
@@ -2391,15 +2252,25 @@
       <c r="Y19" s="4"/>
       <c r="Z19" s="4"/>
     </row>
-    <row r="20" ht="19.5" customHeight="1">
-      <c r="A20" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="3"/>
+    <row r="20" ht="90.0" customHeight="1">
+      <c r="A20" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>80</v>
+      </c>
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
       <c r="I20" s="4"/>
@@ -2421,24 +2292,24 @@
       <c r="Y20" s="4"/>
       <c r="Z20" s="4"/>
     </row>
-    <row r="21" ht="75.0" customHeight="1">
-      <c r="A21" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="B21" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="C21" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="D21" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="E21" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="F21" s="16" t="s">
-        <v>70</v>
+    <row r="21" ht="60.0" customHeight="1">
+      <c r="A21" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>86</v>
       </c>
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
@@ -2461,24 +2332,24 @@
       <c r="Y21" s="4"/>
       <c r="Z21" s="4"/>
     </row>
-    <row r="22" ht="120.0" customHeight="1">
-      <c r="A22" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="B22" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="C22" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="D22" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="E22" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="F22" s="16" t="s">
-        <v>76</v>
+    <row r="22" ht="60.0" customHeight="1">
+      <c r="A22" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>92</v>
       </c>
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
@@ -2501,24 +2372,24 @@
       <c r="Y22" s="4"/>
       <c r="Z22" s="4"/>
     </row>
-    <row r="23" ht="90.0" customHeight="1">
-      <c r="A23" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="B23" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="C23" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="D23" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="E23" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="F23" s="16" t="s">
-        <v>82</v>
+    <row r="23" ht="105.0" customHeight="1">
+      <c r="A23" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>98</v>
       </c>
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
@@ -2542,23 +2413,23 @@
       <c r="Z23" s="4"/>
     </row>
     <row r="24" ht="60.0" customHeight="1">
-      <c r="A24" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="B24" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="C24" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="D24" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="E24" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="F24" s="16" t="s">
-        <v>88</v>
+      <c r="A24" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>104</v>
       </c>
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
@@ -2581,24 +2452,24 @@
       <c r="Y24" s="4"/>
       <c r="Z24" s="4"/>
     </row>
-    <row r="25" ht="60.0" customHeight="1">
-      <c r="A25" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="B25" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="C25" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="D25" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="E25" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="F25" s="16" t="s">
-        <v>94</v>
+    <row r="25" ht="90.0" customHeight="1">
+      <c r="A25" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>110</v>
       </c>
       <c r="G25" s="4"/>
       <c r="H25" s="4"/>
@@ -2621,24 +2492,24 @@
       <c r="Y25" s="4"/>
       <c r="Z25" s="4"/>
     </row>
-    <row r="26" ht="105.0" customHeight="1">
-      <c r="A26" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="B26" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="C26" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="D26" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="E26" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="F26" s="16" t="s">
-        <v>100</v>
+    <row r="26" ht="60.0" customHeight="1">
+      <c r="A26" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>116</v>
       </c>
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
@@ -2661,15 +2532,25 @@
       <c r="Y26" s="4"/>
       <c r="Z26" s="4"/>
     </row>
-    <row r="27" ht="19.5" customHeight="1">
-      <c r="A27" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="3"/>
+    <row r="27" ht="60.0" customHeight="1">
+      <c r="A27" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>122</v>
+      </c>
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>
       <c r="I27" s="4"/>
@@ -2691,24 +2572,24 @@
       <c r="Y27" s="4"/>
       <c r="Z27" s="4"/>
     </row>
-    <row r="28" ht="60.0" customHeight="1">
-      <c r="A28" s="17" t="s">
-        <v>102</v>
-      </c>
-      <c r="B28" s="17" t="s">
-        <v>103</v>
-      </c>
-      <c r="C28" s="17" t="s">
-        <v>104</v>
-      </c>
-      <c r="D28" s="17" t="s">
-        <v>105</v>
-      </c>
-      <c r="E28" s="17" t="s">
-        <v>106</v>
-      </c>
-      <c r="F28" s="17" t="s">
-        <v>107</v>
+    <row r="28" ht="75.0" customHeight="1">
+      <c r="A28" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>128</v>
       </c>
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
@@ -2731,24 +2612,24 @@
       <c r="Y28" s="4"/>
       <c r="Z28" s="4"/>
     </row>
-    <row r="29" ht="90.0" customHeight="1">
-      <c r="A29" s="17" t="s">
-        <v>108</v>
-      </c>
-      <c r="B29" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="C29" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="D29" s="17" t="s">
-        <v>111</v>
-      </c>
-      <c r="E29" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="F29" s="17" t="s">
-        <v>113</v>
+    <row r="29" ht="105.0" customHeight="1">
+      <c r="A29" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>134</v>
       </c>
       <c r="G29" s="4"/>
       <c r="H29" s="4"/>
@@ -2771,24 +2652,24 @@
       <c r="Y29" s="4"/>
       <c r="Z29" s="4"/>
     </row>
-    <row r="30" ht="60.0" customHeight="1">
-      <c r="A30" s="17" t="s">
-        <v>114</v>
-      </c>
-      <c r="B30" s="17" t="s">
-        <v>115</v>
-      </c>
-      <c r="C30" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="D30" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="E30" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="F30" s="17" t="s">
-        <v>119</v>
+    <row r="30" ht="75.0" customHeight="1">
+      <c r="A30" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="F30" s="9" t="s">
+        <v>140</v>
       </c>
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
@@ -2811,134 +2692,144 @@
       <c r="Y30" s="4"/>
       <c r="Z30" s="4"/>
     </row>
-    <row r="31" ht="60.0" customHeight="1">
-      <c r="A31" s="17" t="s">
-        <v>120</v>
-      </c>
-      <c r="B31" s="17" t="s">
-        <v>121</v>
-      </c>
-      <c r="C31" s="17" t="s">
-        <v>122</v>
-      </c>
-      <c r="D31" s="17" t="s">
-        <v>123</v>
-      </c>
-      <c r="E31" s="17" t="s">
-        <v>124</v>
-      </c>
-      <c r="F31" s="17" t="s">
-        <v>125</v>
-      </c>
-      <c r="G31" s="4"/>
-      <c r="H31" s="4"/>
-      <c r="I31" s="4"/>
-      <c r="J31" s="4"/>
-      <c r="K31" s="4"/>
-      <c r="L31" s="4"/>
-      <c r="M31" s="4"/>
-      <c r="N31" s="4"/>
-      <c r="O31" s="4"/>
-      <c r="P31" s="4"/>
-      <c r="Q31" s="4"/>
-      <c r="R31" s="4"/>
-      <c r="S31" s="4"/>
-      <c r="T31" s="4"/>
-      <c r="U31" s="4"/>
-      <c r="V31" s="4"/>
-      <c r="W31" s="4"/>
-      <c r="X31" s="4"/>
-      <c r="Y31" s="4"/>
-      <c r="Z31" s="4"/>
-    </row>
-    <row r="32" ht="75.0" customHeight="1">
-      <c r="A32" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="B32" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="C32" s="17" t="s">
-        <v>128</v>
-      </c>
-      <c r="D32" s="17" t="s">
-        <v>129</v>
-      </c>
-      <c r="E32" s="17" t="s">
-        <v>130</v>
-      </c>
-      <c r="F32" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="G32" s="4"/>
-      <c r="H32" s="4"/>
-      <c r="I32" s="4"/>
-      <c r="J32" s="4"/>
-      <c r="K32" s="4"/>
-      <c r="L32" s="4"/>
-      <c r="M32" s="4"/>
-      <c r="N32" s="4"/>
-      <c r="O32" s="4"/>
-      <c r="P32" s="4"/>
-      <c r="Q32" s="4"/>
-      <c r="R32" s="4"/>
-      <c r="S32" s="4"/>
-      <c r="T32" s="4"/>
-      <c r="U32" s="4"/>
-      <c r="V32" s="4"/>
-      <c r="W32" s="4"/>
-      <c r="X32" s="4"/>
-      <c r="Y32" s="4"/>
-      <c r="Z32" s="4"/>
-    </row>
-    <row r="33" ht="19.5" customHeight="1">
-      <c r="A33" s="15" t="s">
-        <v>132</v>
-      </c>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="4"/>
-      <c r="H33" s="4"/>
-      <c r="I33" s="4"/>
-      <c r="J33" s="4"/>
-      <c r="K33" s="4"/>
-      <c r="L33" s="4"/>
-      <c r="M33" s="4"/>
-      <c r="N33" s="4"/>
-      <c r="O33" s="4"/>
-      <c r="P33" s="4"/>
-      <c r="Q33" s="4"/>
-      <c r="R33" s="4"/>
-      <c r="S33" s="4"/>
-      <c r="T33" s="4"/>
-      <c r="U33" s="4"/>
-      <c r="V33" s="4"/>
-      <c r="W33" s="4"/>
-      <c r="X33" s="4"/>
-      <c r="Y33" s="4"/>
-      <c r="Z33" s="4"/>
-    </row>
-    <row r="34" ht="105.0" customHeight="1">
-      <c r="A34" s="18" t="s">
-        <v>133</v>
-      </c>
-      <c r="B34" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="C34" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="D34" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="E34" s="18" t="s">
-        <v>137</v>
-      </c>
-      <c r="F34" s="18" t="s">
-        <v>138</v>
+    <row r="31" ht="90.0" customHeight="1">
+      <c r="A31" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="D31" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="F31" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="G31" s="14"/>
+      <c r="H31" s="14"/>
+      <c r="I31" s="14"/>
+      <c r="J31" s="14"/>
+      <c r="K31" s="14"/>
+      <c r="L31" s="14"/>
+      <c r="M31" s="14"/>
+      <c r="N31" s="14"/>
+      <c r="O31" s="14"/>
+      <c r="P31" s="14"/>
+      <c r="Q31" s="14"/>
+      <c r="R31" s="14"/>
+      <c r="S31" s="14"/>
+      <c r="T31" s="14"/>
+      <c r="U31" s="14"/>
+      <c r="V31" s="14"/>
+      <c r="W31" s="14"/>
+      <c r="X31" s="14"/>
+      <c r="Y31" s="14"/>
+      <c r="Z31" s="14"/>
+    </row>
+    <row r="32" ht="90.0" customHeight="1">
+      <c r="A32" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="C32" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="D32" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="E32" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="F32" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="G32" s="14"/>
+      <c r="H32" s="14"/>
+      <c r="I32" s="14"/>
+      <c r="J32" s="14"/>
+      <c r="K32" s="14"/>
+      <c r="L32" s="14"/>
+      <c r="M32" s="14"/>
+      <c r="N32" s="14"/>
+      <c r="O32" s="14"/>
+      <c r="P32" s="14"/>
+      <c r="Q32" s="14"/>
+      <c r="R32" s="14"/>
+      <c r="S32" s="14"/>
+      <c r="T32" s="14"/>
+      <c r="U32" s="14"/>
+      <c r="V32" s="14"/>
+      <c r="W32" s="14"/>
+      <c r="X32" s="14"/>
+      <c r="Y32" s="14"/>
+      <c r="Z32" s="14"/>
+    </row>
+    <row r="33" ht="90.0" customHeight="1">
+      <c r="A33" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="B33" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="C33" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="D33" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="E33" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="F33" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="G33" s="16"/>
+      <c r="H33" s="16"/>
+      <c r="I33" s="16"/>
+      <c r="J33" s="16"/>
+      <c r="K33" s="16"/>
+      <c r="L33" s="16"/>
+      <c r="M33" s="16"/>
+      <c r="N33" s="16"/>
+      <c r="O33" s="16"/>
+      <c r="P33" s="16"/>
+      <c r="Q33" s="16"/>
+      <c r="R33" s="16"/>
+      <c r="S33" s="16"/>
+      <c r="T33" s="16"/>
+      <c r="U33" s="16"/>
+      <c r="V33" s="16"/>
+      <c r="W33" s="16"/>
+      <c r="X33" s="16"/>
+      <c r="Y33" s="16"/>
+      <c r="Z33" s="16"/>
+    </row>
+    <row r="34" ht="60.0" customHeight="1">
+      <c r="A34" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="E34" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="F34" s="9" t="s">
+        <v>164</v>
       </c>
       <c r="G34" s="4"/>
       <c r="H34" s="4"/>
@@ -2961,24 +2852,24 @@
       <c r="Y34" s="4"/>
       <c r="Z34" s="4"/>
     </row>
-    <row r="35" ht="75.0" customHeight="1">
-      <c r="A35" s="18" t="s">
-        <v>139</v>
-      </c>
-      <c r="B35" s="18" t="s">
-        <v>140</v>
-      </c>
-      <c r="C35" s="18" t="s">
-        <v>141</v>
-      </c>
-      <c r="D35" s="18" t="s">
-        <v>142</v>
-      </c>
-      <c r="E35" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="F35" s="18" t="s">
-        <v>144</v>
+    <row r="35" ht="60.0" customHeight="1">
+      <c r="A35" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="B35" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="E35" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="F35" s="9" t="s">
+        <v>170</v>
       </c>
       <c r="G35" s="4"/>
       <c r="H35" s="4"/>
@@ -3001,144 +2892,144 @@
       <c r="Y35" s="4"/>
       <c r="Z35" s="4"/>
     </row>
-    <row r="36" ht="90.0" customHeight="1">
-      <c r="A36" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="B36" s="20" t="s">
-        <v>146</v>
-      </c>
-      <c r="C36" s="20" t="s">
-        <v>147</v>
-      </c>
-      <c r="D36" s="21" t="s">
-        <v>148</v>
-      </c>
-      <c r="E36" s="20" t="s">
-        <v>149</v>
-      </c>
-      <c r="F36" s="20" t="s">
-        <v>150</v>
-      </c>
-      <c r="G36" s="22"/>
-      <c r="H36" s="22"/>
-      <c r="I36" s="22"/>
-      <c r="J36" s="22"/>
-      <c r="K36" s="22"/>
-      <c r="L36" s="22"/>
-      <c r="M36" s="22"/>
-      <c r="N36" s="22"/>
-      <c r="O36" s="22"/>
-      <c r="P36" s="22"/>
-      <c r="Q36" s="22"/>
-      <c r="R36" s="22"/>
-      <c r="S36" s="22"/>
-      <c r="T36" s="22"/>
-      <c r="U36" s="22"/>
-      <c r="V36" s="22"/>
-      <c r="W36" s="22"/>
-      <c r="X36" s="22"/>
-      <c r="Y36" s="22"/>
-      <c r="Z36" s="22"/>
-    </row>
-    <row r="37" ht="90.0" customHeight="1">
-      <c r="A37" s="19" t="s">
-        <v>151</v>
-      </c>
-      <c r="B37" s="23" t="s">
-        <v>152</v>
-      </c>
-      <c r="C37" s="23" t="s">
-        <v>153</v>
-      </c>
-      <c r="D37" s="24" t="s">
-        <v>154</v>
-      </c>
-      <c r="E37" s="25" t="s">
-        <v>155</v>
-      </c>
-      <c r="F37" s="23" t="s">
-        <v>156</v>
-      </c>
-      <c r="G37" s="22"/>
-      <c r="H37" s="22"/>
-      <c r="I37" s="22"/>
-      <c r="J37" s="22"/>
-      <c r="K37" s="22"/>
-      <c r="L37" s="22"/>
-      <c r="M37" s="22"/>
-      <c r="N37" s="22"/>
-      <c r="O37" s="22"/>
-      <c r="P37" s="22"/>
-      <c r="Q37" s="22"/>
-      <c r="R37" s="22"/>
-      <c r="S37" s="22"/>
-      <c r="T37" s="22"/>
-      <c r="U37" s="22"/>
-      <c r="V37" s="22"/>
-      <c r="W37" s="22"/>
-      <c r="X37" s="22"/>
-      <c r="Y37" s="22"/>
-      <c r="Z37" s="22"/>
-    </row>
-    <row r="38" ht="90.0" customHeight="1">
-      <c r="A38" s="19" t="s">
-        <v>157</v>
-      </c>
-      <c r="B38" s="23" t="s">
-        <v>158</v>
-      </c>
-      <c r="C38" s="23" t="s">
-        <v>159</v>
-      </c>
-      <c r="D38" s="24" t="s">
-        <v>160</v>
-      </c>
-      <c r="E38" s="25" t="s">
-        <v>161</v>
-      </c>
-      <c r="F38" s="23" t="s">
-        <v>162</v>
-      </c>
-      <c r="G38" s="26"/>
-      <c r="H38" s="26"/>
-      <c r="I38" s="26"/>
-      <c r="J38" s="26"/>
-      <c r="K38" s="26"/>
-      <c r="L38" s="26"/>
-      <c r="M38" s="26"/>
-      <c r="N38" s="26"/>
-      <c r="O38" s="26"/>
-      <c r="P38" s="26"/>
-      <c r="Q38" s="26"/>
-      <c r="R38" s="26"/>
-      <c r="S38" s="26"/>
-      <c r="T38" s="26"/>
-      <c r="U38" s="26"/>
-      <c r="V38" s="26"/>
-      <c r="W38" s="26"/>
-      <c r="X38" s="26"/>
-      <c r="Y38" s="26"/>
-      <c r="Z38" s="26"/>
+    <row r="36" ht="60.0" customHeight="1">
+      <c r="A36" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="B36" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="F36" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
+      <c r="I36" s="4"/>
+      <c r="J36" s="4"/>
+      <c r="K36" s="4"/>
+      <c r="L36" s="4"/>
+      <c r="M36" s="4"/>
+      <c r="N36" s="4"/>
+      <c r="O36" s="4"/>
+      <c r="P36" s="4"/>
+      <c r="Q36" s="4"/>
+      <c r="R36" s="4"/>
+      <c r="S36" s="4"/>
+      <c r="T36" s="4"/>
+      <c r="U36" s="4"/>
+      <c r="V36" s="4"/>
+      <c r="W36" s="4"/>
+      <c r="X36" s="4"/>
+      <c r="Y36" s="4"/>
+      <c r="Z36" s="4"/>
+    </row>
+    <row r="37" ht="75.0" customHeight="1">
+      <c r="A37" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="B37" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="E37" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="F37" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4"/>
+      <c r="K37" s="4"/>
+      <c r="L37" s="4"/>
+      <c r="M37" s="4"/>
+      <c r="N37" s="4"/>
+      <c r="O37" s="4"/>
+      <c r="P37" s="4"/>
+      <c r="Q37" s="4"/>
+      <c r="R37" s="4"/>
+      <c r="S37" s="4"/>
+      <c r="T37" s="4"/>
+      <c r="U37" s="4"/>
+      <c r="V37" s="4"/>
+      <c r="W37" s="4"/>
+      <c r="X37" s="4"/>
+      <c r="Y37" s="4"/>
+      <c r="Z37" s="4"/>
+    </row>
+    <row r="38" ht="60.0" customHeight="1">
+      <c r="A38" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="D38" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="E38" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="F38" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="K38" s="4"/>
+      <c r="L38" s="4"/>
+      <c r="M38" s="4"/>
+      <c r="N38" s="4"/>
+      <c r="O38" s="4"/>
+      <c r="P38" s="4"/>
+      <c r="Q38" s="4"/>
+      <c r="R38" s="4"/>
+      <c r="S38" s="4"/>
+      <c r="T38" s="4"/>
+      <c r="U38" s="4"/>
+      <c r="V38" s="4"/>
+      <c r="W38" s="4"/>
+      <c r="X38" s="4"/>
+      <c r="Y38" s="4"/>
+      <c r="Z38" s="4"/>
     </row>
     <row r="39" ht="60.0" customHeight="1">
-      <c r="A39" s="27" t="s">
-        <v>163</v>
-      </c>
-      <c r="B39" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="C39" s="18" t="s">
-        <v>165</v>
-      </c>
-      <c r="D39" s="18" t="s">
-        <v>166</v>
-      </c>
-      <c r="E39" s="18" t="s">
-        <v>167</v>
-      </c>
-      <c r="F39" s="18" t="s">
-        <v>168</v>
+      <c r="A39" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="E39" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="F39" s="9" t="s">
+        <v>194</v>
       </c>
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
@@ -3161,24 +3052,24 @@
       <c r="Y39" s="4"/>
       <c r="Z39" s="4"/>
     </row>
-    <row r="40" ht="60.0" customHeight="1">
-      <c r="A40" s="27" t="s">
-        <v>169</v>
-      </c>
-      <c r="B40" s="18" t="s">
-        <v>170</v>
-      </c>
-      <c r="C40" s="18" t="s">
-        <v>171</v>
-      </c>
-      <c r="D40" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="E40" s="18" t="s">
-        <v>173</v>
-      </c>
-      <c r="F40" s="18" t="s">
-        <v>174</v>
+    <row r="40" ht="75.0" customHeight="1">
+      <c r="A40" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="B40" s="17" t="s">
+        <v>196</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="D40" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="E40" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="F40" s="9" t="s">
+        <v>200</v>
       </c>
       <c r="G40" s="4"/>
       <c r="H40" s="4"/>
@@ -3201,54 +3092,56 @@
       <c r="Y40" s="4"/>
       <c r="Z40" s="4"/>
     </row>
-    <row r="41" ht="75.0" customHeight="1">
-      <c r="A41" s="28" t="s">
-        <v>175</v>
-      </c>
-      <c r="B41" s="29"/>
-      <c r="C41" s="30"/>
-      <c r="D41" s="30"/>
-      <c r="E41" s="30"/>
-      <c r="F41" s="31"/>
-      <c r="G41" s="32"/>
-      <c r="H41" s="32"/>
-      <c r="I41" s="32"/>
-      <c r="J41" s="32"/>
-      <c r="K41" s="32"/>
-      <c r="L41" s="32"/>
-      <c r="M41" s="32"/>
-      <c r="N41" s="32"/>
-      <c r="O41" s="32"/>
-      <c r="P41" s="32"/>
-      <c r="Q41" s="32"/>
-      <c r="R41" s="32"/>
-      <c r="S41" s="32"/>
-      <c r="T41" s="32"/>
-      <c r="U41" s="32"/>
-      <c r="V41" s="32"/>
-      <c r="W41" s="32"/>
-      <c r="X41" s="32"/>
-      <c r="Y41" s="32"/>
-      <c r="Z41" s="32"/>
-    </row>
-    <row r="42" ht="60.0" customHeight="1">
-      <c r="A42" s="33" t="s">
-        <v>176</v>
-      </c>
-      <c r="B42" s="34" t="s">
-        <v>177</v>
-      </c>
-      <c r="C42" s="34" t="s">
-        <v>178</v>
-      </c>
-      <c r="D42" s="34" t="s">
-        <v>179</v>
-      </c>
-      <c r="E42" s="34" t="s">
-        <v>180</v>
-      </c>
-      <c r="F42" s="34" t="s">
-        <v>181</v>
+    <row r="41" ht="19.5" customHeight="1">
+      <c r="A41" s="18" t="s">
+        <v>201</v>
+      </c>
+      <c r="B41" s="19" t="s">
+        <v>202</v>
+      </c>
+      <c r="C41" s="20"/>
+      <c r="D41" s="20"/>
+      <c r="E41" s="20"/>
+      <c r="F41" s="21"/>
+      <c r="G41" s="22"/>
+      <c r="H41" s="22"/>
+      <c r="I41" s="22"/>
+      <c r="J41" s="22"/>
+      <c r="K41" s="22"/>
+      <c r="L41" s="22"/>
+      <c r="M41" s="22"/>
+      <c r="N41" s="22"/>
+      <c r="O41" s="22"/>
+      <c r="P41" s="22"/>
+      <c r="Q41" s="22"/>
+      <c r="R41" s="22"/>
+      <c r="S41" s="22"/>
+      <c r="T41" s="22"/>
+      <c r="U41" s="22"/>
+      <c r="V41" s="22"/>
+      <c r="W41" s="22"/>
+      <c r="X41" s="22"/>
+      <c r="Y41" s="22"/>
+      <c r="Z41" s="22"/>
+    </row>
+    <row r="42" ht="19.5" customHeight="1">
+      <c r="A42" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B42" s="24" t="s">
+        <v>203</v>
+      </c>
+      <c r="C42" s="23" t="s">
+        <v>204</v>
+      </c>
+      <c r="D42" s="23" t="s">
+        <v>205</v>
+      </c>
+      <c r="E42" s="23" t="s">
+        <v>206</v>
+      </c>
+      <c r="F42" s="23" t="s">
+        <v>207</v>
       </c>
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
@@ -3271,24 +3164,24 @@
       <c r="Y42" s="4"/>
       <c r="Z42" s="4"/>
     </row>
-    <row r="43" ht="75.0" customHeight="1">
-      <c r="A43" s="33" t="s">
-        <v>182</v>
-      </c>
-      <c r="B43" s="34" t="s">
-        <v>183</v>
-      </c>
-      <c r="C43" s="34" t="s">
-        <v>184</v>
-      </c>
-      <c r="D43" s="34" t="s">
-        <v>185</v>
-      </c>
-      <c r="E43" s="34" t="s">
-        <v>186</v>
-      </c>
-      <c r="F43" s="34" t="s">
-        <v>187</v>
+    <row r="43" ht="19.5" customHeight="1">
+      <c r="A43" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="B43" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="E43" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="F43" s="23" t="s">
+        <v>213</v>
       </c>
       <c r="G43" s="4"/>
       <c r="H43" s="4"/>
@@ -3311,24 +3204,24 @@
       <c r="Y43" s="4"/>
       <c r="Z43" s="4"/>
     </row>
-    <row r="44" ht="60.0" customHeight="1">
-      <c r="A44" s="33" t="s">
-        <v>188</v>
-      </c>
-      <c r="B44" s="34" t="s">
-        <v>189</v>
-      </c>
-      <c r="C44" s="34" t="s">
-        <v>190</v>
-      </c>
-      <c r="D44" s="34" t="s">
-        <v>191</v>
-      </c>
-      <c r="E44" s="34" t="s">
-        <v>192</v>
-      </c>
-      <c r="F44" s="34" t="s">
-        <v>193</v>
+    <row r="44" ht="19.5" customHeight="1">
+      <c r="A44" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="B44" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="D44" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="E44" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="F44" s="23" t="s">
+        <v>213</v>
       </c>
       <c r="G44" s="4"/>
       <c r="H44" s="4"/>
@@ -3351,54 +3244,64 @@
       <c r="Y44" s="4"/>
       <c r="Z44" s="4"/>
     </row>
-    <row r="45" ht="60.0" customHeight="1">
-      <c r="A45" s="35" t="s">
-        <v>194</v>
-      </c>
-      <c r="B45" s="36"/>
-      <c r="C45" s="36"/>
-      <c r="D45" s="36"/>
-      <c r="E45" s="36"/>
-      <c r="F45" s="37"/>
-      <c r="G45" s="38"/>
-      <c r="H45" s="38"/>
-      <c r="I45" s="38"/>
-      <c r="J45" s="38"/>
-      <c r="K45" s="38"/>
-      <c r="L45" s="38"/>
-      <c r="M45" s="38"/>
-      <c r="N45" s="38"/>
-      <c r="O45" s="38"/>
-      <c r="P45" s="38"/>
-      <c r="Q45" s="38"/>
-      <c r="R45" s="38"/>
-      <c r="S45" s="38"/>
-      <c r="T45" s="38"/>
-      <c r="U45" s="38"/>
-      <c r="V45" s="38"/>
-      <c r="W45" s="38"/>
-      <c r="X45" s="38"/>
-      <c r="Y45" s="38"/>
-      <c r="Z45" s="38"/>
-    </row>
-    <row r="46" ht="60.0" customHeight="1">
-      <c r="A46" s="39" t="s">
-        <v>195</v>
-      </c>
-      <c r="B46" s="40" t="s">
-        <v>196</v>
-      </c>
-      <c r="C46" s="40" t="s">
-        <v>197</v>
-      </c>
-      <c r="D46" s="40" t="s">
-        <v>198</v>
-      </c>
-      <c r="E46" s="40" t="s">
-        <v>199</v>
-      </c>
-      <c r="F46" s="40" t="s">
-        <v>200</v>
+    <row r="45" ht="19.5" customHeight="1">
+      <c r="A45" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="B45" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="E45" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="F45" s="23" t="s">
+        <v>213</v>
+      </c>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+      <c r="K45" s="4"/>
+      <c r="L45" s="4"/>
+      <c r="M45" s="4"/>
+      <c r="N45" s="4"/>
+      <c r="O45" s="4"/>
+      <c r="P45" s="4"/>
+      <c r="Q45" s="4"/>
+      <c r="R45" s="4"/>
+      <c r="S45" s="4"/>
+      <c r="T45" s="4"/>
+      <c r="U45" s="4"/>
+      <c r="V45" s="4"/>
+      <c r="W45" s="4"/>
+      <c r="X45" s="4"/>
+      <c r="Y45" s="4"/>
+      <c r="Z45" s="4"/>
+    </row>
+    <row r="46" ht="19.5" customHeight="1">
+      <c r="A46" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="B46" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="E46" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="F46" s="23" t="s">
+        <v>226</v>
       </c>
       <c r="G46" s="4"/>
       <c r="H46" s="4"/>
@@ -3421,24 +3324,24 @@
       <c r="Y46" s="4"/>
       <c r="Z46" s="4"/>
     </row>
-    <row r="47" ht="75.0" customHeight="1">
-      <c r="A47" s="39" t="s">
-        <v>201</v>
-      </c>
-      <c r="B47" s="40" t="s">
-        <v>202</v>
-      </c>
-      <c r="C47" s="40" t="s">
-        <v>203</v>
-      </c>
-      <c r="D47" s="40" t="s">
-        <v>204</v>
-      </c>
-      <c r="E47" s="40" t="s">
-        <v>205</v>
-      </c>
-      <c r="F47" s="40" t="s">
-        <v>206</v>
+    <row r="47" ht="19.5" customHeight="1">
+      <c r="A47" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="B47" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="E47" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="F47" s="23" t="s">
+        <v>232</v>
       </c>
       <c r="G47" s="4"/>
       <c r="H47" s="4"/>
@@ -3462,53 +3365,63 @@
       <c r="Z47" s="4"/>
     </row>
     <row r="48" ht="19.5" customHeight="1">
-      <c r="A48" s="41" t="s">
-        <v>207</v>
-      </c>
-      <c r="B48" s="36"/>
-      <c r="C48" s="36"/>
-      <c r="D48" s="36"/>
-      <c r="E48" s="36"/>
-      <c r="F48" s="37"/>
-      <c r="G48" s="38"/>
-      <c r="H48" s="38"/>
-      <c r="I48" s="38"/>
-      <c r="J48" s="38"/>
-      <c r="K48" s="38"/>
-      <c r="L48" s="38"/>
-      <c r="M48" s="38"/>
-      <c r="N48" s="38"/>
-      <c r="O48" s="38"/>
-      <c r="P48" s="38"/>
-      <c r="Q48" s="38"/>
-      <c r="R48" s="38"/>
-      <c r="S48" s="38"/>
-      <c r="T48" s="38"/>
-      <c r="U48" s="38"/>
-      <c r="V48" s="38"/>
-      <c r="W48" s="38"/>
-      <c r="X48" s="38"/>
-      <c r="Y48" s="38"/>
-      <c r="Z48" s="38"/>
+      <c r="A48" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="B48" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="D48" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="E48" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="F48" s="23" t="s">
+        <v>232</v>
+      </c>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+      <c r="K48" s="4"/>
+      <c r="L48" s="4"/>
+      <c r="M48" s="4"/>
+      <c r="N48" s="4"/>
+      <c r="O48" s="4"/>
+      <c r="P48" s="4"/>
+      <c r="Q48" s="4"/>
+      <c r="R48" s="4"/>
+      <c r="S48" s="4"/>
+      <c r="T48" s="4"/>
+      <c r="U48" s="4"/>
+      <c r="V48" s="4"/>
+      <c r="W48" s="4"/>
+      <c r="X48" s="4"/>
+      <c r="Y48" s="4"/>
+      <c r="Z48" s="4"/>
     </row>
     <row r="49" ht="19.5" customHeight="1">
-      <c r="A49" s="42" t="s">
-        <v>15</v>
-      </c>
-      <c r="B49" s="42" t="s">
-        <v>208</v>
-      </c>
-      <c r="C49" s="42" t="s">
-        <v>209</v>
-      </c>
-      <c r="D49" s="42" t="s">
-        <v>210</v>
-      </c>
-      <c r="E49" s="42" t="s">
-        <v>211</v>
-      </c>
-      <c r="F49" s="42" t="s">
-        <v>212</v>
+      <c r="A49" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="B49" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="E49" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="F49" s="23" t="s">
+        <v>232</v>
       </c>
       <c r="G49" s="4"/>
       <c r="H49" s="4"/>
@@ -3532,23 +3445,23 @@
       <c r="Z49" s="4"/>
     </row>
     <row r="50" ht="19.5" customHeight="1">
-      <c r="A50" s="14" t="s">
-        <v>213</v>
-      </c>
-      <c r="B50" s="14" t="s">
-        <v>214</v>
-      </c>
-      <c r="C50" s="14" t="s">
-        <v>215</v>
-      </c>
-      <c r="D50" s="14" t="s">
-        <v>216</v>
-      </c>
-      <c r="E50" s="14" t="s">
-        <v>217</v>
-      </c>
-      <c r="F50" s="43" t="s">
-        <v>218</v>
+      <c r="A50" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="B50" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="C50" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="D50" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="E50" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="F50" s="23" t="s">
+        <v>232</v>
       </c>
       <c r="G50" s="4"/>
       <c r="H50" s="4"/>
@@ -3572,23 +3485,23 @@
       <c r="Z50" s="4"/>
     </row>
     <row r="51" ht="19.5" customHeight="1">
-      <c r="A51" s="14" t="s">
-        <v>219</v>
-      </c>
-      <c r="B51" s="14" t="s">
-        <v>214</v>
-      </c>
-      <c r="C51" s="14" t="s">
-        <v>220</v>
-      </c>
-      <c r="D51" s="14" t="s">
-        <v>221</v>
-      </c>
-      <c r="E51" s="14" t="s">
-        <v>222</v>
-      </c>
-      <c r="F51" s="43" t="s">
-        <v>218</v>
+      <c r="A51" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="B51" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="C51" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="D51" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="E51" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="F51" s="23" t="s">
+        <v>232</v>
       </c>
       <c r="G51" s="4"/>
       <c r="H51" s="4"/>
@@ -3612,23 +3525,23 @@
       <c r="Z51" s="4"/>
     </row>
     <row r="52" ht="19.5" customHeight="1">
-      <c r="A52" s="14" t="s">
-        <v>223</v>
-      </c>
-      <c r="B52" s="14" t="s">
-        <v>214</v>
-      </c>
-      <c r="C52" s="14" t="s">
-        <v>224</v>
-      </c>
-      <c r="D52" s="14" t="s">
-        <v>225</v>
-      </c>
-      <c r="E52" s="14" t="s">
-        <v>226</v>
-      </c>
-      <c r="F52" s="43" t="s">
-        <v>218</v>
+      <c r="A52" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="B52" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="C52" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="D52" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="E52" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="F52" s="23" t="s">
+        <v>213</v>
       </c>
       <c r="G52" s="4"/>
       <c r="H52" s="4"/>
@@ -3652,23 +3565,23 @@
       <c r="Z52" s="4"/>
     </row>
     <row r="53" ht="19.5" customHeight="1">
-      <c r="A53" s="14" t="s">
-        <v>227</v>
-      </c>
-      <c r="B53" s="14" t="s">
-        <v>214</v>
-      </c>
-      <c r="C53" s="14" t="s">
-        <v>228</v>
-      </c>
-      <c r="D53" s="14" t="s">
-        <v>229</v>
-      </c>
-      <c r="E53" s="14" t="s">
-        <v>230</v>
-      </c>
-      <c r="F53" s="44" t="s">
-        <v>231</v>
+      <c r="A53" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="B53" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="C53" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="D53" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="E53" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="F53" s="23" t="s">
+        <v>226</v>
       </c>
       <c r="G53" s="4"/>
       <c r="H53" s="4"/>
@@ -3692,23 +3605,23 @@
       <c r="Z53" s="4"/>
     </row>
     <row r="54" ht="19.5" customHeight="1">
-      <c r="A54" s="18" t="s">
-        <v>232</v>
-      </c>
-      <c r="B54" s="18" t="s">
-        <v>233</v>
-      </c>
-      <c r="C54" s="18" t="s">
-        <v>234</v>
-      </c>
-      <c r="D54" s="18" t="s">
-        <v>235</v>
-      </c>
-      <c r="E54" s="18" t="s">
-        <v>236</v>
-      </c>
-      <c r="F54" s="45" t="s">
-        <v>237</v>
+      <c r="A54" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="B54" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="C54" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="D54" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="E54" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="F54" s="23" t="s">
+        <v>226</v>
       </c>
       <c r="G54" s="4"/>
       <c r="H54" s="4"/>
@@ -3732,23 +3645,23 @@
       <c r="Z54" s="4"/>
     </row>
     <row r="55" ht="19.5" customHeight="1">
-      <c r="A55" s="18" t="s">
-        <v>238</v>
-      </c>
-      <c r="B55" s="18" t="s">
-        <v>233</v>
-      </c>
-      <c r="C55" s="18" t="s">
-        <v>239</v>
-      </c>
-      <c r="D55" s="18" t="s">
-        <v>240</v>
-      </c>
-      <c r="E55" s="18" t="s">
-        <v>241</v>
-      </c>
-      <c r="F55" s="45" t="s">
-        <v>237</v>
+      <c r="A55" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="B55" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="C55" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="D55" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="E55" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="F55" s="23" t="s">
+        <v>232</v>
       </c>
       <c r="G55" s="4"/>
       <c r="H55" s="4"/>
@@ -3772,23 +3685,23 @@
       <c r="Z55" s="4"/>
     </row>
     <row r="56" ht="19.5" customHeight="1">
-      <c r="A56" s="18" t="s">
-        <v>242</v>
-      </c>
-      <c r="B56" s="18" t="s">
-        <v>233</v>
-      </c>
-      <c r="C56" s="18" t="s">
-        <v>243</v>
-      </c>
-      <c r="D56" s="18" t="s">
-        <v>244</v>
-      </c>
-      <c r="E56" s="18" t="s">
-        <v>245</v>
-      </c>
-      <c r="F56" s="45" t="s">
-        <v>237</v>
+      <c r="A56" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="B56" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="C56" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="D56" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="E56" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="F56" s="23" t="s">
+        <v>213</v>
       </c>
       <c r="G56" s="4"/>
       <c r="H56" s="4"/>
@@ -3812,23 +3725,23 @@
       <c r="Z56" s="4"/>
     </row>
     <row r="57" ht="19.5" customHeight="1">
-      <c r="A57" s="18" t="s">
-        <v>246</v>
-      </c>
-      <c r="B57" s="18" t="s">
-        <v>233</v>
-      </c>
-      <c r="C57" s="18" t="s">
-        <v>247</v>
-      </c>
-      <c r="D57" s="18" t="s">
-        <v>248</v>
-      </c>
-      <c r="E57" s="18" t="s">
-        <v>249</v>
-      </c>
-      <c r="F57" s="45" t="s">
-        <v>237</v>
+      <c r="A57" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="B57" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="C57" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="D57" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="E57" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="F57" s="23" t="s">
+        <v>213</v>
       </c>
       <c r="G57" s="4"/>
       <c r="H57" s="4"/>
@@ -3852,23 +3765,23 @@
       <c r="Z57" s="4"/>
     </row>
     <row r="58" ht="19.5" customHeight="1">
-      <c r="A58" s="18" t="s">
-        <v>250</v>
-      </c>
-      <c r="B58" s="18" t="s">
-        <v>233</v>
-      </c>
-      <c r="C58" s="18" t="s">
-        <v>251</v>
-      </c>
-      <c r="D58" s="18" t="s">
-        <v>252</v>
-      </c>
-      <c r="E58" s="18" t="s">
-        <v>253</v>
-      </c>
-      <c r="F58" s="45" t="s">
-        <v>237</v>
+      <c r="A58" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="B58" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="C58" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="D58" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="E58" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="F58" s="23" t="s">
+        <v>213</v>
       </c>
       <c r="G58" s="4"/>
       <c r="H58" s="4"/>
@@ -3892,23 +3805,23 @@
       <c r="Z58" s="4"/>
     </row>
     <row r="59" ht="19.5" customHeight="1">
-      <c r="A59" s="16" t="s">
-        <v>254</v>
-      </c>
-      <c r="B59" s="16" t="s">
-        <v>255</v>
-      </c>
-      <c r="C59" s="16" t="s">
-        <v>256</v>
-      </c>
-      <c r="D59" s="16" t="s">
-        <v>257</v>
-      </c>
-      <c r="E59" s="16" t="s">
-        <v>258</v>
-      </c>
-      <c r="F59" s="43" t="s">
-        <v>218</v>
+      <c r="A59" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="B59" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="C59" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="D59" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="E59" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="F59" s="23" t="s">
+        <v>226</v>
       </c>
       <c r="G59" s="4"/>
       <c r="H59" s="4"/>
@@ -3932,23 +3845,23 @@
       <c r="Z59" s="4"/>
     </row>
     <row r="60" ht="19.5" customHeight="1">
-      <c r="A60" s="16" t="s">
-        <v>259</v>
-      </c>
-      <c r="B60" s="16" t="s">
-        <v>255</v>
-      </c>
-      <c r="C60" s="16" t="s">
-        <v>260</v>
-      </c>
-      <c r="D60" s="16" t="s">
-        <v>261</v>
-      </c>
-      <c r="E60" s="16" t="s">
-        <v>262</v>
-      </c>
-      <c r="F60" s="44" t="s">
-        <v>231</v>
+      <c r="A60" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="B60" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="C60" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="D60" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="E60" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="F60" s="23" t="s">
+        <v>226</v>
       </c>
       <c r="G60" s="4"/>
       <c r="H60" s="4"/>
@@ -3972,23 +3885,23 @@
       <c r="Z60" s="4"/>
     </row>
     <row r="61" ht="19.5" customHeight="1">
-      <c r="A61" s="16" t="s">
-        <v>263</v>
-      </c>
-      <c r="B61" s="16" t="s">
-        <v>255</v>
-      </c>
-      <c r="C61" s="16" t="s">
-        <v>264</v>
-      </c>
-      <c r="D61" s="16" t="s">
-        <v>265</v>
-      </c>
-      <c r="E61" s="16" t="s">
-        <v>266</v>
-      </c>
-      <c r="F61" s="44" t="s">
-        <v>231</v>
+      <c r="A61" s="9" t="s">
+        <v>288</v>
+      </c>
+      <c r="B61" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="C61" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="D61" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="E61" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="F61" s="23" t="s">
+        <v>213</v>
       </c>
       <c r="G61" s="4"/>
       <c r="H61" s="4"/>
@@ -4011,24 +3924,24 @@
       <c r="Y61" s="4"/>
       <c r="Z61" s="4"/>
     </row>
-    <row r="62" ht="19.5" customHeight="1">
-      <c r="A62" s="17" t="s">
-        <v>267</v>
-      </c>
-      <c r="B62" s="17" t="s">
-        <v>268</v>
-      </c>
-      <c r="C62" s="17" t="s">
-        <v>269</v>
-      </c>
-      <c r="D62" s="17" t="s">
-        <v>270</v>
-      </c>
-      <c r="E62" s="17" t="s">
-        <v>271</v>
-      </c>
-      <c r="F62" s="45" t="s">
-        <v>237</v>
+    <row r="62" ht="15.75" customHeight="1">
+      <c r="A62" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="B62" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="C62" s="9" t="s">
+        <v>293</v>
+      </c>
+      <c r="D62" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="E62" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="F62" s="23" t="s">
+        <v>213</v>
       </c>
       <c r="G62" s="4"/>
       <c r="H62" s="4"/>
@@ -4051,25 +3964,13 @@
       <c r="Y62" s="4"/>
       <c r="Z62" s="4"/>
     </row>
-    <row r="63" ht="19.5" customHeight="1">
-      <c r="A63" s="17" t="s">
-        <v>272</v>
-      </c>
-      <c r="B63" s="17" t="s">
-        <v>268</v>
-      </c>
-      <c r="C63" s="17" t="s">
-        <v>273</v>
-      </c>
-      <c r="D63" s="17" t="s">
-        <v>274</v>
-      </c>
-      <c r="E63" s="17" t="s">
-        <v>275</v>
-      </c>
-      <c r="F63" s="43" t="s">
-        <v>218</v>
-      </c>
+    <row r="63" ht="15.75" customHeight="1">
+      <c r="A63" s="25"/>
+      <c r="B63" s="25"/>
+      <c r="C63" s="25"/>
+      <c r="D63" s="25"/>
+      <c r="E63" s="25"/>
+      <c r="F63" s="25"/>
       <c r="G63" s="4"/>
       <c r="H63" s="4"/>
       <c r="I63" s="4"/>
@@ -4091,25 +3992,13 @@
       <c r="Y63" s="4"/>
       <c r="Z63" s="4"/>
     </row>
-    <row r="64" ht="19.5" customHeight="1">
-      <c r="A64" s="17" t="s">
-        <v>276</v>
-      </c>
-      <c r="B64" s="17" t="s">
-        <v>268</v>
-      </c>
-      <c r="C64" s="17" t="s">
-        <v>277</v>
-      </c>
-      <c r="D64" s="17" t="s">
-        <v>278</v>
-      </c>
-      <c r="E64" s="17" t="s">
-        <v>279</v>
-      </c>
-      <c r="F64" s="43" t="s">
-        <v>218</v>
-      </c>
+    <row r="64" ht="15.75" customHeight="1">
+      <c r="A64" s="25"/>
+      <c r="B64" s="25"/>
+      <c r="C64" s="25"/>
+      <c r="D64" s="25"/>
+      <c r="E64" s="25"/>
+      <c r="F64" s="25"/>
       <c r="G64" s="4"/>
       <c r="H64" s="4"/>
       <c r="I64" s="4"/>
@@ -4131,25 +4020,13 @@
       <c r="Y64" s="4"/>
       <c r="Z64" s="4"/>
     </row>
-    <row r="65" ht="19.5" customHeight="1">
-      <c r="A65" s="17" t="s">
-        <v>280</v>
-      </c>
-      <c r="B65" s="17" t="s">
-        <v>268</v>
-      </c>
-      <c r="C65" s="17" t="s">
-        <v>281</v>
-      </c>
-      <c r="D65" s="17" t="s">
-        <v>282</v>
-      </c>
-      <c r="E65" s="17" t="s">
-        <v>283</v>
-      </c>
-      <c r="F65" s="43" t="s">
-        <v>218</v>
-      </c>
+    <row r="65" ht="15.75" customHeight="1">
+      <c r="A65" s="25"/>
+      <c r="B65" s="25"/>
+      <c r="C65" s="25"/>
+      <c r="D65" s="25"/>
+      <c r="E65" s="25"/>
+      <c r="F65" s="25"/>
       <c r="G65" s="4"/>
       <c r="H65" s="4"/>
       <c r="I65" s="4"/>
@@ -4171,25 +4048,13 @@
       <c r="Y65" s="4"/>
       <c r="Z65" s="4"/>
     </row>
-    <row r="66" ht="19.5" customHeight="1">
-      <c r="A66" s="34" t="s">
-        <v>284</v>
-      </c>
-      <c r="B66" s="34" t="s">
-        <v>285</v>
-      </c>
-      <c r="C66" s="34" t="s">
-        <v>286</v>
-      </c>
-      <c r="D66" s="34" t="s">
-        <v>287</v>
-      </c>
-      <c r="E66" s="34" t="s">
-        <v>288</v>
-      </c>
-      <c r="F66" s="44" t="s">
-        <v>231</v>
-      </c>
+    <row r="66" ht="15.75" customHeight="1">
+      <c r="A66" s="25"/>
+      <c r="B66" s="25"/>
+      <c r="C66" s="25"/>
+      <c r="D66" s="25"/>
+      <c r="E66" s="25"/>
+      <c r="F66" s="25"/>
       <c r="G66" s="4"/>
       <c r="H66" s="4"/>
       <c r="I66" s="4"/>
@@ -4211,25 +4076,13 @@
       <c r="Y66" s="4"/>
       <c r="Z66" s="4"/>
     </row>
-    <row r="67" ht="19.5" customHeight="1">
-      <c r="A67" s="34" t="s">
-        <v>289</v>
-      </c>
-      <c r="B67" s="34" t="s">
-        <v>285</v>
-      </c>
-      <c r="C67" s="34" t="s">
-        <v>290</v>
-      </c>
-      <c r="D67" s="34" t="s">
-        <v>291</v>
-      </c>
-      <c r="E67" s="34" t="s">
-        <v>292</v>
-      </c>
-      <c r="F67" s="44" t="s">
-        <v>231</v>
-      </c>
+    <row r="67" ht="15.75" customHeight="1">
+      <c r="A67" s="25"/>
+      <c r="B67" s="25"/>
+      <c r="C67" s="25"/>
+      <c r="D67" s="25"/>
+      <c r="E67" s="25"/>
+      <c r="F67" s="25"/>
       <c r="G67" s="4"/>
       <c r="H67" s="4"/>
       <c r="I67" s="4"/>
@@ -4251,25 +4104,13 @@
       <c r="Y67" s="4"/>
       <c r="Z67" s="4"/>
     </row>
-    <row r="68" ht="19.5" customHeight="1">
-      <c r="A68" s="40" t="s">
-        <v>293</v>
-      </c>
-      <c r="B68" s="40" t="s">
-        <v>294</v>
-      </c>
-      <c r="C68" s="40" t="s">
-        <v>295</v>
-      </c>
-      <c r="D68" s="40" t="s">
-        <v>296</v>
-      </c>
-      <c r="E68" s="40" t="s">
-        <v>297</v>
-      </c>
-      <c r="F68" s="43" t="s">
-        <v>218</v>
-      </c>
+    <row r="68" ht="15.75" customHeight="1">
+      <c r="A68" s="25"/>
+      <c r="B68" s="25"/>
+      <c r="C68" s="25"/>
+      <c r="D68" s="25"/>
+      <c r="E68" s="25"/>
+      <c r="F68" s="25"/>
       <c r="G68" s="4"/>
       <c r="H68" s="4"/>
       <c r="I68" s="4"/>
@@ -4292,24 +4133,12 @@
       <c r="Z68" s="4"/>
     </row>
     <row r="69" ht="15.75" customHeight="1">
-      <c r="A69" s="40" t="s">
-        <v>298</v>
-      </c>
-      <c r="B69" s="40" t="s">
-        <v>294</v>
-      </c>
-      <c r="C69" s="40" t="s">
-        <v>299</v>
-      </c>
-      <c r="D69" s="40" t="s">
-        <v>300</v>
-      </c>
-      <c r="E69" s="40" t="s">
-        <v>301</v>
-      </c>
-      <c r="F69" s="43" t="s">
-        <v>218</v>
-      </c>
+      <c r="A69" s="25"/>
+      <c r="B69" s="25"/>
+      <c r="C69" s="25"/>
+      <c r="D69" s="25"/>
+      <c r="E69" s="25"/>
+      <c r="F69" s="25"/>
       <c r="G69" s="4"/>
       <c r="H69" s="4"/>
       <c r="I69" s="4"/>
@@ -4332,12 +4161,12 @@
       <c r="Z69" s="4"/>
     </row>
     <row r="70" ht="15.75" customHeight="1">
-      <c r="A70" s="4"/>
-      <c r="B70" s="4"/>
-      <c r="C70" s="4"/>
-      <c r="D70" s="4"/>
-      <c r="E70" s="4"/>
-      <c r="F70" s="4"/>
+      <c r="A70" s="25"/>
+      <c r="B70" s="25"/>
+      <c r="C70" s="25"/>
+      <c r="D70" s="25"/>
+      <c r="E70" s="25"/>
+      <c r="F70" s="25"/>
       <c r="G70" s="4"/>
       <c r="H70" s="4"/>
       <c r="I70" s="4"/>
@@ -4360,12 +4189,12 @@
       <c r="Z70" s="4"/>
     </row>
     <row r="71" ht="15.75" customHeight="1">
-      <c r="A71" s="4"/>
-      <c r="B71" s="4"/>
-      <c r="C71" s="4"/>
-      <c r="D71" s="4"/>
-      <c r="E71" s="4"/>
-      <c r="F71" s="4"/>
+      <c r="A71" s="25"/>
+      <c r="B71" s="25"/>
+      <c r="C71" s="25"/>
+      <c r="D71" s="25"/>
+      <c r="E71" s="25"/>
+      <c r="F71" s="25"/>
       <c r="G71" s="4"/>
       <c r="H71" s="4"/>
       <c r="I71" s="4"/>
@@ -4388,12 +4217,12 @@
       <c r="Z71" s="4"/>
     </row>
     <row r="72" ht="15.75" customHeight="1">
-      <c r="A72" s="4"/>
-      <c r="B72" s="4"/>
-      <c r="C72" s="4"/>
-      <c r="D72" s="4"/>
-      <c r="E72" s="4"/>
-      <c r="F72" s="4"/>
+      <c r="A72" s="25"/>
+      <c r="B72" s="25"/>
+      <c r="C72" s="25"/>
+      <c r="D72" s="25"/>
+      <c r="E72" s="25"/>
+      <c r="F72" s="25"/>
       <c r="G72" s="4"/>
       <c r="H72" s="4"/>
       <c r="I72" s="4"/>
@@ -4416,12 +4245,12 @@
       <c r="Z72" s="4"/>
     </row>
     <row r="73" ht="15.75" customHeight="1">
-      <c r="A73" s="4"/>
-      <c r="B73" s="4"/>
-      <c r="C73" s="4"/>
-      <c r="D73" s="4"/>
-      <c r="E73" s="4"/>
-      <c r="F73" s="4"/>
+      <c r="A73" s="25"/>
+      <c r="B73" s="25"/>
+      <c r="C73" s="25"/>
+      <c r="D73" s="25"/>
+      <c r="E73" s="25"/>
+      <c r="F73" s="25"/>
       <c r="G73" s="4"/>
       <c r="H73" s="4"/>
       <c r="I73" s="4"/>
@@ -4444,12 +4273,12 @@
       <c r="Z73" s="4"/>
     </row>
     <row r="74" ht="15.75" customHeight="1">
-      <c r="A74" s="4"/>
-      <c r="B74" s="4"/>
-      <c r="C74" s="4"/>
-      <c r="D74" s="4"/>
-      <c r="E74" s="4"/>
-      <c r="F74" s="4"/>
+      <c r="A74" s="25"/>
+      <c r="B74" s="25"/>
+      <c r="C74" s="25"/>
+      <c r="D74" s="25"/>
+      <c r="E74" s="25"/>
+      <c r="F74" s="25"/>
       <c r="G74" s="4"/>
       <c r="H74" s="4"/>
       <c r="I74" s="4"/>
@@ -4472,12 +4301,12 @@
       <c r="Z74" s="4"/>
     </row>
     <row r="75" ht="15.75" customHeight="1">
-      <c r="A75" s="4"/>
-      <c r="B75" s="4"/>
-      <c r="C75" s="4"/>
-      <c r="D75" s="4"/>
-      <c r="E75" s="4"/>
-      <c r="F75" s="4"/>
+      <c r="A75" s="25"/>
+      <c r="B75" s="25"/>
+      <c r="C75" s="25"/>
+      <c r="D75" s="25"/>
+      <c r="E75" s="25"/>
+      <c r="F75" s="25"/>
       <c r="G75" s="4"/>
       <c r="H75" s="4"/>
       <c r="I75" s="4"/>
@@ -4500,12 +4329,12 @@
       <c r="Z75" s="4"/>
     </row>
     <row r="76" ht="15.75" customHeight="1">
-      <c r="A76" s="4"/>
-      <c r="B76" s="4"/>
-      <c r="C76" s="4"/>
-      <c r="D76" s="4"/>
-      <c r="E76" s="4"/>
-      <c r="F76" s="4"/>
+      <c r="A76" s="25"/>
+      <c r="B76" s="25"/>
+      <c r="C76" s="25"/>
+      <c r="D76" s="25"/>
+      <c r="E76" s="25"/>
+      <c r="F76" s="25"/>
       <c r="G76" s="4"/>
       <c r="H76" s="4"/>
       <c r="I76" s="4"/>
@@ -4528,12 +4357,12 @@
       <c r="Z76" s="4"/>
     </row>
     <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="4"/>
-      <c r="B77" s="4"/>
-      <c r="C77" s="4"/>
-      <c r="D77" s="4"/>
-      <c r="E77" s="4"/>
-      <c r="F77" s="4"/>
+      <c r="A77" s="25"/>
+      <c r="B77" s="25"/>
+      <c r="C77" s="25"/>
+      <c r="D77" s="25"/>
+      <c r="E77" s="25"/>
+      <c r="F77" s="25"/>
       <c r="G77" s="4"/>
       <c r="H77" s="4"/>
       <c r="I77" s="4"/>
@@ -4556,12 +4385,12 @@
       <c r="Z77" s="4"/>
     </row>
     <row r="78" ht="15.75" customHeight="1">
-      <c r="A78" s="4"/>
-      <c r="B78" s="4"/>
-      <c r="C78" s="4"/>
-      <c r="D78" s="4"/>
-      <c r="E78" s="4"/>
-      <c r="F78" s="4"/>
+      <c r="A78" s="25"/>
+      <c r="B78" s="25"/>
+      <c r="C78" s="25"/>
+      <c r="D78" s="25"/>
+      <c r="E78" s="25"/>
+      <c r="F78" s="25"/>
       <c r="G78" s="4"/>
       <c r="H78" s="4"/>
       <c r="I78" s="4"/>
@@ -4584,12 +4413,12 @@
       <c r="Z78" s="4"/>
     </row>
     <row r="79" ht="15.75" customHeight="1">
-      <c r="A79" s="4"/>
-      <c r="B79" s="4"/>
-      <c r="C79" s="4"/>
-      <c r="D79" s="4"/>
-      <c r="E79" s="4"/>
-      <c r="F79" s="4"/>
+      <c r="A79" s="25"/>
+      <c r="B79" s="25"/>
+      <c r="C79" s="25"/>
+      <c r="D79" s="25"/>
+      <c r="E79" s="25"/>
+      <c r="F79" s="25"/>
       <c r="G79" s="4"/>
       <c r="H79" s="4"/>
       <c r="I79" s="4"/>
@@ -4612,12 +4441,12 @@
       <c r="Z79" s="4"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
-      <c r="A80" s="4"/>
-      <c r="B80" s="4"/>
-      <c r="C80" s="4"/>
-      <c r="D80" s="4"/>
-      <c r="E80" s="4"/>
-      <c r="F80" s="4"/>
+      <c r="A80" s="25"/>
+      <c r="B80" s="25"/>
+      <c r="C80" s="25"/>
+      <c r="D80" s="25"/>
+      <c r="E80" s="25"/>
+      <c r="F80" s="25"/>
       <c r="G80" s="4"/>
       <c r="H80" s="4"/>
       <c r="I80" s="4"/>
@@ -4640,12 +4469,12 @@
       <c r="Z80" s="4"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
-      <c r="A81" s="4"/>
-      <c r="B81" s="4"/>
-      <c r="C81" s="4"/>
-      <c r="D81" s="4"/>
-      <c r="E81" s="4"/>
-      <c r="F81" s="4"/>
+      <c r="A81" s="25"/>
+      <c r="B81" s="25"/>
+      <c r="C81" s="25"/>
+      <c r="D81" s="25"/>
+      <c r="E81" s="25"/>
+      <c r="F81" s="25"/>
       <c r="G81" s="4"/>
       <c r="H81" s="4"/>
       <c r="I81" s="4"/>
@@ -4668,12 +4497,12 @@
       <c r="Z81" s="4"/>
     </row>
     <row r="82" ht="15.75" customHeight="1">
-      <c r="A82" s="4"/>
-      <c r="B82" s="4"/>
-      <c r="C82" s="4"/>
-      <c r="D82" s="4"/>
-      <c r="E82" s="4"/>
-      <c r="F82" s="4"/>
+      <c r="A82" s="25"/>
+      <c r="B82" s="25"/>
+      <c r="C82" s="25"/>
+      <c r="D82" s="25"/>
+      <c r="E82" s="25"/>
+      <c r="F82" s="25"/>
       <c r="G82" s="4"/>
       <c r="H82" s="4"/>
       <c r="I82" s="4"/>
@@ -4696,12 +4525,12 @@
       <c r="Z82" s="4"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
-      <c r="A83" s="4"/>
-      <c r="B83" s="4"/>
-      <c r="C83" s="4"/>
-      <c r="D83" s="4"/>
-      <c r="E83" s="4"/>
-      <c r="F83" s="4"/>
+      <c r="A83" s="25"/>
+      <c r="B83" s="25"/>
+      <c r="C83" s="25"/>
+      <c r="D83" s="25"/>
+      <c r="E83" s="25"/>
+      <c r="F83" s="25"/>
       <c r="G83" s="4"/>
       <c r="H83" s="4"/>
       <c r="I83" s="4"/>
@@ -4724,12 +4553,12 @@
       <c r="Z83" s="4"/>
     </row>
     <row r="84" ht="15.75" customHeight="1">
-      <c r="A84" s="4"/>
-      <c r="B84" s="4"/>
-      <c r="C84" s="4"/>
-      <c r="D84" s="4"/>
-      <c r="E84" s="4"/>
-      <c r="F84" s="4"/>
+      <c r="A84" s="25"/>
+      <c r="B84" s="25"/>
+      <c r="C84" s="25"/>
+      <c r="D84" s="25"/>
+      <c r="E84" s="25"/>
+      <c r="F84" s="25"/>
       <c r="G84" s="4"/>
       <c r="H84" s="4"/>
       <c r="I84" s="4"/>
@@ -4752,12 +4581,12 @@
       <c r="Z84" s="4"/>
     </row>
     <row r="85" ht="15.75" customHeight="1">
-      <c r="A85" s="4"/>
-      <c r="B85" s="4"/>
-      <c r="C85" s="4"/>
-      <c r="D85" s="4"/>
-      <c r="E85" s="4"/>
-      <c r="F85" s="4"/>
+      <c r="A85" s="25"/>
+      <c r="B85" s="25"/>
+      <c r="C85" s="25"/>
+      <c r="D85" s="25"/>
+      <c r="E85" s="25"/>
+      <c r="F85" s="25"/>
       <c r="G85" s="4"/>
       <c r="H85" s="4"/>
       <c r="I85" s="4"/>
@@ -4780,12 +4609,12 @@
       <c r="Z85" s="4"/>
     </row>
     <row r="86" ht="15.75" customHeight="1">
-      <c r="A86" s="4"/>
-      <c r="B86" s="4"/>
-      <c r="C86" s="4"/>
-      <c r="D86" s="4"/>
-      <c r="E86" s="4"/>
-      <c r="F86" s="4"/>
+      <c r="A86" s="25"/>
+      <c r="B86" s="25"/>
+      <c r="C86" s="25"/>
+      <c r="D86" s="25"/>
+      <c r="E86" s="25"/>
+      <c r="F86" s="25"/>
       <c r="G86" s="4"/>
       <c r="H86" s="4"/>
       <c r="I86" s="4"/>
@@ -4808,12 +4637,12 @@
       <c r="Z86" s="4"/>
     </row>
     <row r="87" ht="15.75" customHeight="1">
-      <c r="A87" s="4"/>
-      <c r="B87" s="4"/>
-      <c r="C87" s="4"/>
-      <c r="D87" s="4"/>
-      <c r="E87" s="4"/>
-      <c r="F87" s="4"/>
+      <c r="A87" s="25"/>
+      <c r="B87" s="25"/>
+      <c r="C87" s="25"/>
+      <c r="D87" s="25"/>
+      <c r="E87" s="25"/>
+      <c r="F87" s="25"/>
       <c r="G87" s="4"/>
       <c r="H87" s="4"/>
       <c r="I87" s="4"/>
@@ -4836,12 +4665,12 @@
       <c r="Z87" s="4"/>
     </row>
     <row r="88" ht="15.75" customHeight="1">
-      <c r="A88" s="4"/>
-      <c r="B88" s="4"/>
-      <c r="C88" s="4"/>
-      <c r="D88" s="4"/>
-      <c r="E88" s="4"/>
-      <c r="F88" s="4"/>
+      <c r="A88" s="26"/>
+      <c r="B88" s="26"/>
+      <c r="C88" s="26"/>
+      <c r="D88" s="26"/>
+      <c r="E88" s="26"/>
+      <c r="F88" s="26"/>
       <c r="G88" s="4"/>
       <c r="H88" s="4"/>
       <c r="I88" s="4"/>
@@ -4864,12 +4693,12 @@
       <c r="Z88" s="4"/>
     </row>
     <row r="89" ht="15.75" customHeight="1">
-      <c r="A89" s="4"/>
-      <c r="B89" s="4"/>
-      <c r="C89" s="4"/>
-      <c r="D89" s="4"/>
-      <c r="E89" s="4"/>
-      <c r="F89" s="4"/>
+      <c r="A89" s="27"/>
+      <c r="B89" s="27"/>
+      <c r="C89" s="27"/>
+      <c r="D89" s="27"/>
+      <c r="E89" s="27"/>
+      <c r="F89" s="27"/>
       <c r="G89" s="4"/>
       <c r="H89" s="4"/>
       <c r="I89" s="4"/>
@@ -4892,12 +4721,12 @@
       <c r="Z89" s="4"/>
     </row>
     <row r="90" ht="15.75" customHeight="1">
-      <c r="A90" s="4"/>
-      <c r="B90" s="4"/>
-      <c r="C90" s="4"/>
-      <c r="D90" s="4"/>
-      <c r="E90" s="4"/>
-      <c r="F90" s="4"/>
+      <c r="A90" s="27"/>
+      <c r="B90" s="27"/>
+      <c r="C90" s="27"/>
+      <c r="D90" s="27"/>
+      <c r="E90" s="27"/>
+      <c r="F90" s="27"/>
       <c r="G90" s="4"/>
       <c r="H90" s="4"/>
       <c r="I90" s="4"/>
@@ -4920,12 +4749,12 @@
       <c r="Z90" s="4"/>
     </row>
     <row r="91" ht="15.75" customHeight="1">
-      <c r="A91" s="4"/>
-      <c r="B91" s="4"/>
-      <c r="C91" s="4"/>
-      <c r="D91" s="4"/>
-      <c r="E91" s="4"/>
-      <c r="F91" s="4"/>
+      <c r="A91" s="27"/>
+      <c r="B91" s="27"/>
+      <c r="C91" s="27"/>
+      <c r="D91" s="27"/>
+      <c r="E91" s="27"/>
+      <c r="F91" s="27"/>
       <c r="G91" s="4"/>
       <c r="H91" s="4"/>
       <c r="I91" s="4"/>
@@ -4948,12 +4777,12 @@
       <c r="Z91" s="4"/>
     </row>
     <row r="92" ht="15.75" customHeight="1">
-      <c r="A92" s="4"/>
-      <c r="B92" s="4"/>
-      <c r="C92" s="4"/>
-      <c r="D92" s="4"/>
-      <c r="E92" s="4"/>
-      <c r="F92" s="4"/>
+      <c r="A92" s="27"/>
+      <c r="B92" s="27"/>
+      <c r="C92" s="27"/>
+      <c r="D92" s="27"/>
+      <c r="E92" s="27"/>
+      <c r="F92" s="27"/>
       <c r="G92" s="4"/>
       <c r="H92" s="4"/>
       <c r="I92" s="4"/>
@@ -4976,12 +4805,12 @@
       <c r="Z92" s="4"/>
     </row>
     <row r="93" ht="15.75" customHeight="1">
-      <c r="A93" s="4"/>
-      <c r="B93" s="4"/>
-      <c r="C93" s="4"/>
-      <c r="D93" s="4"/>
-      <c r="E93" s="4"/>
-      <c r="F93" s="4"/>
+      <c r="A93" s="27"/>
+      <c r="B93" s="27"/>
+      <c r="C93" s="27"/>
+      <c r="D93" s="27"/>
+      <c r="E93" s="27"/>
+      <c r="F93" s="27"/>
       <c r="G93" s="4"/>
       <c r="H93" s="4"/>
       <c r="I93" s="4"/>
@@ -5004,12 +4833,12 @@
       <c r="Z93" s="4"/>
     </row>
     <row r="94" ht="15.75" customHeight="1">
-      <c r="A94" s="4"/>
-      <c r="B94" s="4"/>
-      <c r="C94" s="4"/>
-      <c r="D94" s="4"/>
-      <c r="E94" s="4"/>
-      <c r="F94" s="4"/>
+      <c r="A94" s="27"/>
+      <c r="B94" s="27"/>
+      <c r="C94" s="27"/>
+      <c r="D94" s="27"/>
+      <c r="E94" s="27"/>
+      <c r="F94" s="27"/>
       <c r="G94" s="4"/>
       <c r="H94" s="4"/>
       <c r="I94" s="4"/>
@@ -5032,12 +4861,12 @@
       <c r="Z94" s="4"/>
     </row>
     <row r="95" ht="15.75" customHeight="1">
-      <c r="A95" s="4"/>
-      <c r="B95" s="4"/>
-      <c r="C95" s="4"/>
-      <c r="D95" s="4"/>
-      <c r="E95" s="4"/>
-      <c r="F95" s="4"/>
+      <c r="A95" s="27"/>
+      <c r="B95" s="27"/>
+      <c r="C95" s="27"/>
+      <c r="D95" s="27"/>
+      <c r="E95" s="27"/>
+      <c r="F95" s="27"/>
       <c r="G95" s="4"/>
       <c r="H95" s="4"/>
       <c r="I95" s="4"/>
@@ -5060,12 +4889,12 @@
       <c r="Z95" s="4"/>
     </row>
     <row r="96" ht="15.75" customHeight="1">
-      <c r="A96" s="4"/>
-      <c r="B96" s="4"/>
-      <c r="C96" s="4"/>
-      <c r="D96" s="4"/>
-      <c r="E96" s="4"/>
-      <c r="F96" s="4"/>
+      <c r="A96" s="27"/>
+      <c r="B96" s="27"/>
+      <c r="C96" s="27"/>
+      <c r="D96" s="27"/>
+      <c r="E96" s="27"/>
+      <c r="F96" s="27"/>
       <c r="G96" s="4"/>
       <c r="H96" s="4"/>
       <c r="I96" s="4"/>
@@ -5088,12 +4917,12 @@
       <c r="Z96" s="4"/>
     </row>
     <row r="97" ht="15.75" customHeight="1">
-      <c r="A97" s="4"/>
-      <c r="B97" s="4"/>
-      <c r="C97" s="4"/>
-      <c r="D97" s="4"/>
-      <c r="E97" s="4"/>
-      <c r="F97" s="4"/>
+      <c r="A97" s="27"/>
+      <c r="B97" s="27"/>
+      <c r="C97" s="27"/>
+      <c r="D97" s="27"/>
+      <c r="E97" s="27"/>
+      <c r="F97" s="27"/>
       <c r="G97" s="4"/>
       <c r="H97" s="4"/>
       <c r="I97" s="4"/>
@@ -5116,12 +4945,12 @@
       <c r="Z97" s="4"/>
     </row>
     <row r="98" ht="15.75" customHeight="1">
-      <c r="A98" s="4"/>
-      <c r="B98" s="4"/>
-      <c r="C98" s="4"/>
-      <c r="D98" s="4"/>
-      <c r="E98" s="4"/>
-      <c r="F98" s="4"/>
+      <c r="A98" s="27"/>
+      <c r="B98" s="27"/>
+      <c r="C98" s="27"/>
+      <c r="D98" s="27"/>
+      <c r="E98" s="27"/>
+      <c r="F98" s="27"/>
       <c r="G98" s="4"/>
       <c r="H98" s="4"/>
       <c r="I98" s="4"/>
@@ -5144,12 +4973,12 @@
       <c r="Z98" s="4"/>
     </row>
     <row r="99" ht="15.75" customHeight="1">
-      <c r="A99" s="4"/>
-      <c r="B99" s="4"/>
-      <c r="C99" s="4"/>
-      <c r="D99" s="4"/>
-      <c r="E99" s="4"/>
-      <c r="F99" s="4"/>
+      <c r="A99" s="27"/>
+      <c r="B99" s="27"/>
+      <c r="C99" s="27"/>
+      <c r="D99" s="27"/>
+      <c r="E99" s="27"/>
+      <c r="F99" s="27"/>
       <c r="G99" s="4"/>
       <c r="H99" s="4"/>
       <c r="I99" s="4"/>
@@ -9742,26 +9571,6 @@
       <c r="D263" s="4"/>
       <c r="E263" s="4"/>
       <c r="F263" s="4"/>
-      <c r="G263" s="4"/>
-      <c r="H263" s="4"/>
-      <c r="I263" s="4"/>
-      <c r="J263" s="4"/>
-      <c r="K263" s="4"/>
-      <c r="L263" s="4"/>
-      <c r="M263" s="4"/>
-      <c r="N263" s="4"/>
-      <c r="O263" s="4"/>
-      <c r="P263" s="4"/>
-      <c r="Q263" s="4"/>
-      <c r="R263" s="4"/>
-      <c r="S263" s="4"/>
-      <c r="T263" s="4"/>
-      <c r="U263" s="4"/>
-      <c r="V263" s="4"/>
-      <c r="W263" s="4"/>
-      <c r="X263" s="4"/>
-      <c r="Y263" s="4"/>
-      <c r="Z263" s="4"/>
     </row>
     <row r="264" ht="15.75" customHeight="1">
       <c r="A264" s="4"/>
@@ -9770,26 +9579,6 @@
       <c r="D264" s="4"/>
       <c r="E264" s="4"/>
       <c r="F264" s="4"/>
-      <c r="G264" s="4"/>
-      <c r="H264" s="4"/>
-      <c r="I264" s="4"/>
-      <c r="J264" s="4"/>
-      <c r="K264" s="4"/>
-      <c r="L264" s="4"/>
-      <c r="M264" s="4"/>
-      <c r="N264" s="4"/>
-      <c r="O264" s="4"/>
-      <c r="P264" s="4"/>
-      <c r="Q264" s="4"/>
-      <c r="R264" s="4"/>
-      <c r="S264" s="4"/>
-      <c r="T264" s="4"/>
-      <c r="U264" s="4"/>
-      <c r="V264" s="4"/>
-      <c r="W264" s="4"/>
-      <c r="X264" s="4"/>
-      <c r="Y264" s="4"/>
-      <c r="Z264" s="4"/>
     </row>
     <row r="265" ht="15.75" customHeight="1">
       <c r="A265" s="4"/>
@@ -9798,26 +9587,6 @@
       <c r="D265" s="4"/>
       <c r="E265" s="4"/>
       <c r="F265" s="4"/>
-      <c r="G265" s="4"/>
-      <c r="H265" s="4"/>
-      <c r="I265" s="4"/>
-      <c r="J265" s="4"/>
-      <c r="K265" s="4"/>
-      <c r="L265" s="4"/>
-      <c r="M265" s="4"/>
-      <c r="N265" s="4"/>
-      <c r="O265" s="4"/>
-      <c r="P265" s="4"/>
-      <c r="Q265" s="4"/>
-      <c r="R265" s="4"/>
-      <c r="S265" s="4"/>
-      <c r="T265" s="4"/>
-      <c r="U265" s="4"/>
-      <c r="V265" s="4"/>
-      <c r="W265" s="4"/>
-      <c r="X265" s="4"/>
-      <c r="Y265" s="4"/>
-      <c r="Z265" s="4"/>
     </row>
     <row r="266" ht="15.75" customHeight="1">
       <c r="A266" s="4"/>
@@ -9826,26 +9595,6 @@
       <c r="D266" s="4"/>
       <c r="E266" s="4"/>
       <c r="F266" s="4"/>
-      <c r="G266" s="4"/>
-      <c r="H266" s="4"/>
-      <c r="I266" s="4"/>
-      <c r="J266" s="4"/>
-      <c r="K266" s="4"/>
-      <c r="L266" s="4"/>
-      <c r="M266" s="4"/>
-      <c r="N266" s="4"/>
-      <c r="O266" s="4"/>
-      <c r="P266" s="4"/>
-      <c r="Q266" s="4"/>
-      <c r="R266" s="4"/>
-      <c r="S266" s="4"/>
-      <c r="T266" s="4"/>
-      <c r="U266" s="4"/>
-      <c r="V266" s="4"/>
-      <c r="W266" s="4"/>
-      <c r="X266" s="4"/>
-      <c r="Y266" s="4"/>
-      <c r="Z266" s="4"/>
     </row>
     <row r="267" ht="15.75" customHeight="1">
       <c r="A267" s="4"/>
@@ -9854,26 +9603,6 @@
       <c r="D267" s="4"/>
       <c r="E267" s="4"/>
       <c r="F267" s="4"/>
-      <c r="G267" s="4"/>
-      <c r="H267" s="4"/>
-      <c r="I267" s="4"/>
-      <c r="J267" s="4"/>
-      <c r="K267" s="4"/>
-      <c r="L267" s="4"/>
-      <c r="M267" s="4"/>
-      <c r="N267" s="4"/>
-      <c r="O267" s="4"/>
-      <c r="P267" s="4"/>
-      <c r="Q267" s="4"/>
-      <c r="R267" s="4"/>
-      <c r="S267" s="4"/>
-      <c r="T267" s="4"/>
-      <c r="U267" s="4"/>
-      <c r="V267" s="4"/>
-      <c r="W267" s="4"/>
-      <c r="X267" s="4"/>
-      <c r="Y267" s="4"/>
-      <c r="Z267" s="4"/>
     </row>
     <row r="268" ht="15.75" customHeight="1">
       <c r="A268" s="4"/>
@@ -9882,26 +9611,6 @@
       <c r="D268" s="4"/>
       <c r="E268" s="4"/>
       <c r="F268" s="4"/>
-      <c r="G268" s="4"/>
-      <c r="H268" s="4"/>
-      <c r="I268" s="4"/>
-      <c r="J268" s="4"/>
-      <c r="K268" s="4"/>
-      <c r="L268" s="4"/>
-      <c r="M268" s="4"/>
-      <c r="N268" s="4"/>
-      <c r="O268" s="4"/>
-      <c r="P268" s="4"/>
-      <c r="Q268" s="4"/>
-      <c r="R268" s="4"/>
-      <c r="S268" s="4"/>
-      <c r="T268" s="4"/>
-      <c r="U268" s="4"/>
-      <c r="V268" s="4"/>
-      <c r="W268" s="4"/>
-      <c r="X268" s="4"/>
-      <c r="Y268" s="4"/>
-      <c r="Z268" s="4"/>
     </row>
     <row r="269" ht="15.75" customHeight="1">
       <c r="A269" s="4"/>
@@ -9910,26 +9619,6 @@
       <c r="D269" s="4"/>
       <c r="E269" s="4"/>
       <c r="F269" s="4"/>
-      <c r="G269" s="4"/>
-      <c r="H269" s="4"/>
-      <c r="I269" s="4"/>
-      <c r="J269" s="4"/>
-      <c r="K269" s="4"/>
-      <c r="L269" s="4"/>
-      <c r="M269" s="4"/>
-      <c r="N269" s="4"/>
-      <c r="O269" s="4"/>
-      <c r="P269" s="4"/>
-      <c r="Q269" s="4"/>
-      <c r="R269" s="4"/>
-      <c r="S269" s="4"/>
-      <c r="T269" s="4"/>
-      <c r="U269" s="4"/>
-      <c r="V269" s="4"/>
-      <c r="W269" s="4"/>
-      <c r="X269" s="4"/>
-      <c r="Y269" s="4"/>
-      <c r="Z269" s="4"/>
     </row>
     <row r="270" ht="15.75" customHeight="1">
       <c r="A270" s="4"/>
@@ -15715,64 +15404,10 @@
       <c r="E992" s="4"/>
       <c r="F992" s="4"/>
     </row>
-    <row r="993" ht="15.75" customHeight="1">
-      <c r="A993" s="4"/>
-      <c r="B993" s="4"/>
-      <c r="C993" s="4"/>
-      <c r="D993" s="4"/>
-      <c r="E993" s="4"/>
-      <c r="F993" s="4"/>
-    </row>
-    <row r="994" ht="15.75" customHeight="1">
-      <c r="A994" s="4"/>
-      <c r="B994" s="4"/>
-      <c r="C994" s="4"/>
-      <c r="D994" s="4"/>
-      <c r="E994" s="4"/>
-      <c r="F994" s="4"/>
-    </row>
-    <row r="995" ht="15.75" customHeight="1">
-      <c r="A995" s="4"/>
-      <c r="B995" s="4"/>
-      <c r="C995" s="4"/>
-      <c r="D995" s="4"/>
-      <c r="E995" s="4"/>
-      <c r="F995" s="4"/>
-    </row>
-    <row r="996" ht="15.75" customHeight="1">
-      <c r="A996" s="4"/>
-      <c r="B996" s="4"/>
-      <c r="C996" s="4"/>
-      <c r="D996" s="4"/>
-      <c r="E996" s="4"/>
-      <c r="F996" s="4"/>
-    </row>
-    <row r="997" ht="15.75" customHeight="1">
-      <c r="A997" s="4"/>
-      <c r="B997" s="4"/>
-      <c r="C997" s="4"/>
-      <c r="D997" s="4"/>
-      <c r="E997" s="4"/>
-      <c r="F997" s="4"/>
-    </row>
-    <row r="998" ht="15.75" customHeight="1">
-      <c r="A998" s="4"/>
-      <c r="B998" s="4"/>
-      <c r="C998" s="4"/>
-      <c r="D998" s="4"/>
-      <c r="E998" s="4"/>
-      <c r="F998" s="4"/>
-    </row>
-    <row r="999" ht="15.75" customHeight="1">
-      <c r="A999" s="4"/>
-      <c r="B999" s="4"/>
-      <c r="C999" s="4"/>
-      <c r="D999" s="4"/>
-      <c r="E999" s="4"/>
-      <c r="F999" s="4"/>
-    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="9">
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="A9:F9"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="B3:F3"/>
@@ -15780,12 +15415,6 @@
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="B7:F7"/>
-    <mergeCell ref="B8:F8"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A12:F12"/>
-    <mergeCell ref="A20:F20"/>
-    <mergeCell ref="A27:F27"/>
-    <mergeCell ref="A33:F33"/>
   </mergeCells>
   <printOptions/>
   <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
